--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487678_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487678_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2029</v>
+        <v>8.073499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0985</v>
+        <v>5.642</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1044</v>
+        <v>2.4315</v>
       </c>
       <c r="G2" t="n">
         <v>2.9738</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8127</v>
+        <v>1.0579</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1384</v>
+        <v>0.4051</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3257</v>
+        <v>0.6528</v>
       </c>
       <c r="V2" t="n">
         <v>4.2358</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.647</v>
+        <v>3.3044</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9409</v>
+        <v>1.5926</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7061</v>
+        <v>1.7118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.657</v>
+        <v>4.1361</v>
       </c>
       <c r="H3" t="n">
-        <v>1.202</v>
+        <v>1.4212</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.545</v>
+        <v>2.7149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4243</v>
+        <v>3.9205</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4243</v>
+        <v>1.3223</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.5982</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2327</v>
+        <v>0.2156</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.0989</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.545</v>
+        <v>0.1168</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9527</v>
+        <v>0.4579</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4569</v>
+        <v>0.5139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4958</v>
+        <v>-0.0561</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0373</v>
+        <v>-0.7075</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>-0.7075</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0502</v>
+        <v>2.7554</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4759</v>
+        <v>1.3218</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5743</v>
+        <v>1.4336</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7346</v>
+        <v>0.657</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4098</v>
+        <v>1.202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3248</v>
+        <v>-0.545</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3445</v>
+        <v>0.4243</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2811</v>
+        <v>0.4243</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0634</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3901</v>
+        <v>0.2327</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1287</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2614</v>
+        <v>-0.545</v>
       </c>
       <c r="P4" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1642</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6857</v>
+        <v>1.061</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7896</v>
+        <v>0.8378</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1038</v>
+        <v>0.2232</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5642</v>
+        <v>1.0373</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0701</v>
+        <v>-0.1865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8688</v>
+        <v>2.7405</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1422</v>
+        <v>1.9754</v>
       </c>
       <c r="F5" t="n">
-        <v>3.011</v>
+        <v>0.7651</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8048999999999999</v>
+        <v>2.7346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3411</v>
+        <v>2.4098</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4638</v>
+        <v>0.3248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6291</v>
+        <v>1.3445</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5355</v>
+        <v>1.2811</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1646</v>
+        <v>0.0634</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1758</v>
+        <v>1.3901</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8766</v>
+        <v>1.1287</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7008</v>
+        <v>0.2614</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0747</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3284</v>
+        <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>5.0818</v>
+        <v>0.376</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3512</v>
+        <v>0.2891</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7306</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2716</v>
+        <v>-0.5642</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0478</v>
+        <v>1.506</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>-2.0701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5798</v>
+        <v>1.642</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0316</v>
+        <v>-0.8331</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5483</v>
+        <v>2.4751</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1361</v>
+        <v>0.3124</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4212</v>
+        <v>0.4119</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7149</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9205</v>
+        <v>-0.6542</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3223</v>
+        <v>0.1071</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5982</v>
+        <v>-0.7613</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2156</v>
+        <v>0.9666</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0989</v>
+        <v>0.3048</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1168</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1344</v>
+        <v>-1.3582</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2667</v>
+        <v>0.1057</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0471</v>
+        <v>-0.0446</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2196</v>
+        <v>0.1503</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7075</v>
+        <v>1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7075</v>
+        <v>1.2239</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.196</v>
+        <v>0.3638</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3336</v>
+        <v>-2.1021</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5296</v>
+        <v>2.4659</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3124</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4119</v>
+        <v>0.3411</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.4638</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6542</v>
+        <v>0.6291</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1071</v>
+        <v>-0.5355</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7613</v>
+        <v>1.1646</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9666</v>
+        <v>0.1758</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3048</v>
+        <v>0.8766</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.7008</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3582</v>
+        <v>-4.0747</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3403</v>
+        <v>2.5768</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5451</v>
+        <v>1.3913</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2048</v>
+        <v>1.1856</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2239</v>
+        <v>-1.2716</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2239</v>
+        <v>-0.0478</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0337</v>
+        <v>0.0936</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0206</v>
+        <v>0.1207</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0543</v>
+        <v>-0.0271</v>
       </c>
       <c r="G9" t="n">
         <v>0.08160000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1153</v>
+        <v>0.0121</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.4637</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4257</v>
+        <v>-1.2651</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7468</v>
+        <v>0.8013</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6859</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3035</v>
+        <v>-0.0883</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2423</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0612</v>
+        <v>-0.0067</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8229</v>
+        <v>-1.3436</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2137</v>
+        <v>-2.6526</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3908</v>
+        <v>1.309</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6409</v>
@@ -1312,13 +1312,13 @@
         <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7342</v>
+        <v>-0.2549</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7874</v>
+        <v>-0.2263</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0532</v>
+        <v>-0.0286</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5337</v>
+        <v>-3.6246</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0571</v>
+        <v>-3.8754</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5234</v>
+        <v>0.2508</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1958</v>
@@ -1390,13 +1390,13 @@
         <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8726</v>
+        <v>0.7817</v>
       </c>
       <c r="T12" t="n">
-        <v>0.074</v>
+        <v>0.2557</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7986</v>
+        <v>0.526</v>
       </c>
       <c r="V12" t="n">
         <v>0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1815</v>
+        <v>-6.036</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6074</v>
+        <v>-3.9252</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5741</v>
+        <v>-2.1108</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7976</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4302</v>
+        <v>0.7153</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1077</v>
+        <v>0.5745</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3225</v>
+        <v>0.1408</v>
       </c>
       <c r="V13" t="n">
         <v>-3.9537</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.488</v>
+        <v>7.699299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.212199999999999</v>
+        <v>-4.001</v>
       </c>
       <c r="F14" t="n">
-        <v>11.7003</v>
+        <v>11.7002</v>
       </c>
       <c r="G14" t="n">
         <v>6.513699999999999</v>
@@ -1522,10 +1522,10 @@
         <v>3.6902</v>
       </c>
       <c r="K14" t="n">
-        <v>4.218299999999998</v>
+        <v>4.218299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5281000000000002</v>
+        <v>-0.5281000000000007</v>
       </c>
       <c r="M14" t="n">
         <v>2.823399999999999</v>
@@ -1546,19 +1546,19 @@
         <v>14.5525</v>
       </c>
       <c r="S14" t="n">
-        <v>5.456400000000001</v>
+        <v>6.667699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8037</v>
+        <v>4.015000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6528</v>
+        <v>2.652700000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.601499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>6.726799999999999</v>
+        <v>6.7268</v>
       </c>
       <c r="X14" t="n">
         <v>-8.328199999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0681</v>
+        <v>5.1842</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5463</v>
+        <v>1.4472</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5218</v>
+        <v>3.737</v>
       </c>
       <c r="G15" t="n">
         <v>3.29</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8622</v>
+        <v>-0.7461</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2719</v>
+        <v>-0.371</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5904</v>
+        <v>-0.3751</v>
       </c>
       <c r="V15" t="n">
         <v>0.894</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0543</v>
+        <v>1.5172</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.321</v>
+        <v>-1.0217</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3753</v>
+        <v>2.5389</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5810999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.666</v>
+        <v>-1.2032</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0022</v>
+        <v>-0.6985</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6682</v>
+        <v>-0.5047</v>
       </c>
       <c r="V16" t="n">
         <v>3.1075</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6312</v>
+        <v>0.7012</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8162</v>
+        <v>-3.1165</v>
       </c>
       <c r="F17" t="n">
-        <v>4.4474</v>
+        <v>3.8178</v>
       </c>
       <c r="G17" t="n">
         <v>0.2319</v>
@@ -1780,13 +1780,13 @@
         <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1871</v>
+        <v>0.2571</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.2375</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1243</v>
+        <v>0.4947</v>
       </c>
       <c r="V17" t="n">
         <v>0.0182</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0218</v>
+        <v>0.6859</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6085</v>
+        <v>3.109</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5866</v>
+        <v>-2.4231</v>
       </c>
       <c r="G18" t="n">
         <v>2.0002</v>
@@ -1858,13 +1858,13 @@
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4607</v>
+        <v>0.2033</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3028</v>
+        <v>0.1977</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1579</v>
+        <v>0.0056</v>
       </c>
       <c r="V18" t="n">
         <v>-2.0997</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2329</v>
+        <v>-0.2956</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0425</v>
+        <v>-1.7307</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2754</v>
+        <v>1.4351</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.285</v>
+        <v>-0.6848</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1582</v>
+        <v>-0.8066</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1268</v>
+        <v>0.1218</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6073</v>
+        <v>-0.271</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4449</v>
+        <v>-0.276</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1624</v>
+        <v>0.005</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8923</v>
+        <v>-0.4138</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6031</v>
+        <v>-0.5306</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2892</v>
+        <v>0.1168</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1999</v>
+        <v>-1.3066</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1233</v>
+        <v>-0.4896</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0765</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.506</v>
+        <v>0.7257</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.788</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ALONSO GONZÁLEZ</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7648</v>
+        <v>-0.7451</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7885</v>
+        <v>-0.3579</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0236</v>
+        <v>-0.3873</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9398</v>
+        <v>-0.285</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1335</v>
+        <v>-0.1582</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0733</v>
+        <v>-0.1268</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6673</v>
+        <v>0.6073</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.4449</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6673</v>
+        <v>0.1624</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2725</v>
+        <v>-0.8923</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1335</v>
+        <v>-0.6031</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.406</v>
+        <v>-0.2892</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.3582</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>0.109</v>
+        <v>-0.3124</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1211</v>
+        <v>-0.2771</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2302</v>
+        <v>-0.0353</v>
       </c>
       <c r="V20" t="n">
-        <v>0.066</v>
+        <v>-1.506</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0.066</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>M. ALONSO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2749</v>
+        <v>-0.8739</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3313</v>
+        <v>-0.7885</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0564</v>
+        <v>-0.0854</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6848</v>
+        <v>-0.9398</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8066</v>
+        <v>0.1335</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1218</v>
+        <v>-1.0733</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.271</v>
+        <v>-0.6673</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.276</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.005</v>
+        <v>-0.6673</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4138</v>
+        <v>-0.2725</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5306</v>
+        <v>0.1335</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1168</v>
+        <v>-0.406</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.286</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0902</v>
+        <v>-0.1211</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1958</v>
+        <v>0.1211</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7257</v>
+        <v>0.066</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7257</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4462</v>
+        <v>-1.9139</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7516</v>
+        <v>-1.3628</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3053</v>
+        <v>-0.5511</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2656</v>
+        <v>0.5674</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9353</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3303</v>
+        <v>1.4036</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5295</v>
+        <v>0.7582</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9433</v>
+        <v>-0.5232</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5861</v>
+        <v>1.2813</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7362</v>
+        <v>-0.1908</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.992</v>
+        <v>-0.3131</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2558</v>
+        <v>0.1223</v>
       </c>
       <c r="P22" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1344</v>
+        <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6254</v>
+        <v>-0.2574</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1541</v>
+        <v>-0.1806</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5642</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2682</v>
+        <v>-2.2653</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3628</v>
+        <v>-2.6524</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9054</v>
+        <v>0.3871</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5674</v>
+        <v>-2.2656</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-1.9353</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4036</v>
+        <v>-0.3303</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7582</v>
+        <v>-1.5295</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5232</v>
+        <v>-0.9433</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2813</v>
+        <v>-0.5861</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1908</v>
+        <v>-0.7362</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3131</v>
+        <v>-0.992</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1223</v>
+        <v>0.2558</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5523</v>
+        <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6117</v>
+        <v>-0.1938</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1806</v>
+        <v>0.2532</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4311</v>
+        <v>-0.4469</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8358</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8341</v>
+        <v>-3.5249</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7813</v>
+        <v>-1.5811</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0528</v>
+        <v>-1.9438</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7859</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8605</v>
+        <v>-0.5513</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7268</v>
+        <v>-0.5266</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1337</v>
+        <v>-0.0247</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1579</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4423</v>
+        <v>-4.2905</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.745</v>
+        <v>-3.6449</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6972</v>
+        <v>-0.6455</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0608</v>
@@ -2404,13 +2404,13 @@
         <v>1.9403</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8306</v>
+        <v>-0.6788</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3017</v>
+        <v>-0.2016</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5289</v>
+        <v>-0.4772</v>
       </c>
       <c r="V25" t="n">
         <v>3.3895</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.488</v>
+        <v>-5.8207</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.7004</v>
+        <v>-11.7003</v>
       </c>
       <c r="F26" t="n">
-        <v>5.212400000000001</v>
+        <v>5.879700000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-6.513500000000001</v>
@@ -2461,7 +2461,7 @@
         <v>-4.3251</v>
       </c>
       <c r="L26" t="n">
-        <v>1.501800000000001</v>
+        <v>1.5018</v>
       </c>
       <c r="M26" t="n">
         <v>-3.6904</v>
@@ -2482,13 +2482,13 @@
         <v>18.4332</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.456300000000001</v>
+        <v>-4.7892</v>
       </c>
       <c r="T26" t="n">
         <v>-2.6527</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8037</v>
+        <v>-2.1363</v>
       </c>
       <c r="V26" t="n">
         <v>1.6015</v>
